--- a/public/templates/000_pm_suite/02_프로젝트 개발/01_컨설팅/02_제안작업/프로젝트명_제안계획서_V1.0_20230530.xlsx
+++ b/public/templates/000_pm_suite/02_프로젝트 개발/01_컨설팅/02_제안작업/프로젝트명_제안계획서_V1.0_20230530.xlsx
@@ -529,7 +529,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-30] 한빛글로벌 SyncGuard AI 입찰 제안서 작성 계획서 (Proposal Work Plan) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-30] 한빛글로벌 SyncFlow AI 입찰 제안서 작성 계획서 (Proposal Work Plan) — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>핵심 작성 내용 (SyncGuard AI 차별화 포인트)</t>
+          <t>핵심 작성 내용 (SyncFlow AI 차별화 포인트)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>한빛글로벌 표시·광고 수기 심의 병목 분석 및 심의 리드타임 85% 단축 전략</t>
+          <t>한빛글로벌 계약·기술규격 수기 검증 병목 분석 및 검증 리드타임 85% 단축 전략</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>100대 규제 룰셋 엔진, 전성분 배합한도 자동 대조, 대체문구 추천, FO/BO 28개 화면</t>
+          <t>100대 규제 룰셋 엔진, 자재BOM 유해물질한도 자동 대조, 표준수정조항 추천, FO/BO 28개 화면</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>50문항 골든셋 정밀도 96.4% 실증, 전성분 기밀 격리, 시큐어코딩 49개 약점 진단</t>
+          <t>50문항 골든셋 정밀도 96.4% 시험검증, 자재BOM 기밀 격리, 시큐어코딩 49개 약점 진단</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
